--- a/spring-flower/ku/excel/report.xlsx
+++ b/spring-flower/ku/excel/report.xlsx
@@ -95,7 +95,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:D7"/>
+  <dimension ref="A1:D4"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <sheetData>
     <row r="1">
@@ -111,7 +111,7 @@
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
-          <t>年龄</t>
+          <t>电话</t>
         </is>
       </c>
       <c r="D1" s="1" t="inlineStr">
@@ -124,109 +124,37 @@
       <c r="A2" s="2" t="n">
         <v>1.0</v>
       </c>
-      <c r="B2" s="2" t="inlineStr">
+      <c r="B2" s="2"/>
+      <c r="C2" s="2" t="inlineStr">
         <is>
-          <t>张三1</t>
+          <t>13900001001</t>
         </is>
       </c>
-      <c r="C2" s="2" t="n">
-        <v>21.0</v>
-      </c>
-      <c r="D2" s="2" t="inlineStr">
-        <is>
-          <t>zhangsan1@qq.com</t>
-        </is>
-      </c>
+      <c r="D2" s="2"/>
     </row>
     <row r="3">
       <c r="A3" s="2" t="n">
         <v>2.0</v>
       </c>
-      <c r="B3" s="2" t="inlineStr">
+      <c r="B3" s="2"/>
+      <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>张三2</t>
+          <t>13900001002</t>
         </is>
       </c>
-      <c r="C3" s="2" t="n">
-        <v>22.0</v>
-      </c>
-      <c r="D3" s="2" t="inlineStr">
-        <is>
-          <t>zhangsan2@qq.com</t>
-        </is>
-      </c>
+      <c r="D3" s="2"/>
     </row>
     <row r="4">
       <c r="A4" s="2" t="n">
         <v>3.0</v>
       </c>
-      <c r="B4" s="2" t="inlineStr">
+      <c r="B4" s="2"/>
+      <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>张三3</t>
+          <t>13900001003</t>
         </is>
       </c>
-      <c r="C4" s="2" t="n">
-        <v>23.0</v>
-      </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>zhangsan3@qq.com</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="2" t="n">
-        <v>4.0</v>
-      </c>
-      <c r="B5" s="2" t="inlineStr">
-        <is>
-          <t>张三4</t>
-        </is>
-      </c>
-      <c r="C5" s="2" t="n">
-        <v>24.0</v>
-      </c>
-      <c r="D5" s="2" t="inlineStr">
-        <is>
-          <t>zhangsan4@qq.com</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="2" t="n">
-        <v>5.0</v>
-      </c>
-      <c r="B6" s="2" t="inlineStr">
-        <is>
-          <t>张三5</t>
-        </is>
-      </c>
-      <c r="C6" s="2" t="n">
-        <v>25.0</v>
-      </c>
-      <c r="D6" s="2" t="inlineStr">
-        <is>
-          <t>zhangsan5@qq.com</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="2" t="n">
-        <v>6.0</v>
-      </c>
-      <c r="B7" s="2" t="inlineStr">
-        <is>
-          <t>张三6</t>
-        </is>
-      </c>
-      <c r="C7" s="2" t="n">
-        <v>26.0</v>
-      </c>
-      <c r="D7" s="2" t="inlineStr">
-        <is>
-          <t>zhangsan6@qq.com</t>
-        </is>
-      </c>
+      <c r="D4" s="2"/>
     </row>
   </sheetData>
   <mergeCells count="1">
